--- a/Систематический_обзор_3.5_29_09.xlsx
+++ b/Систематический_обзор_3.5_29_09.xlsx
@@ -300,10 +300,10 @@
     <t>n/a</t>
   </si>
   <si>
-    <t xml:space="preserve">The authors argue that empirical evidence on gamification remains limited in the grocery sector, because most prior studies examine airlines, hospitality and general e-commerce, where loyalty is tied to aspirational rewards. Section 2.4 formulates four gaps. First, no controlled experimental study has examined gamification specifically in online grocery retail, a domain defined by high purchase frequency, low involvement per transaction and strong sensitivity to price and convenience. Second, frameworks such as Self-Determination Theory and Flow Theory offer mechanistic explanations, yet empirical evidence testing these mechanisms within grocery contexts remains absent. Third, demographic moderators, particularly age and gender, have been largely ignored in prior gamification research despite well-documented differences in digital engagement. Fourth, the reviewed studies are predominantly quantitative, leaving the experiential and psychological dimensions of gamified grocery loyalty poorly understood. The introduction adds two unresolved questions, whether game mechanics that encourage exploration and social competition conflict with the utilitarian, time-sensitive nature of grocery shopping, and whether gamification drives actual purchasing behaviour or merely increases platform dwell time. Table 1 assigns a specific contextual limitation to every reviewed study and positions the present research as addressing these gaps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High relevance, suitable as the anchor source for the theoretical model. The study tests the same independent variable as our RQ, namely game mechanics (challenges, badges, progress bars, leaderboards) built into an app-based loyalty programme, in an adjacent digital food context, and it supplies a ready-made causal chain. Gamification does not raise purchases directly but operates through engagement (usage to engagement β = 0.028, p &lt; 0.001; engagement to purchase frequency β = 0.042, p &lt; 0.001; the direct effect appears only when engagement is removed from the model). The 15-item engagement index actually captures attitudinal loyalty (emotional attachment, trust, satisfaction, enjoyment, willingness to recommend, α = 0.93 and 0.91), while purchase frequency captures behavioural loyalty, so the measurement logic transfers to food delivery apps with minimal adaptation. Three propositions can be carried over. The effect is stronger for younger users, as the gamification by age interaction is significant. The engagement to purchase link shows diminishing returns, implying an optimal level of gamification before fatigue. Dwell time belongs in the model as a control rather than an outcome, since more app time does not automatically produce more purchases. Two cautions apply. The abstract and conclusion present gender as a moderator, but the regression reports no significant gender interaction and only descriptive differences, so gender should be used as an exploratory moderator. The setting is planned grocery baskets in a UK panel over two months rather than impulse-driven food delivery with heavy multi-homing, so the transfer is analogical and novelty effects cannot be separated from habit.</t>
+    <t xml:space="preserve">Limited empirical evidence on gamification in the grocery sector; most prior studies examine airlines, hospitality and general e-commerce, where loyalty is tied to aspirational rewards. No controlled experimental study of gamification in online grocery retail, and the mechanisms proposed by Self-Determination Theory and Flow Theory remain empirically untested there. Demographic moderators (age, gender) largely ignored in prior gamification research; previous studies predominantly quantitative, leaving the experiential and psychological dimensions poorly understood. It remains unclear whether gamification drives actual purchasing behaviour or merely increases platform dwell time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highly relevant. The article directly investigates how game mechanics (challenges, badges, progress bars, leaderboards) in a loyalty app affect consumer engagement and repeat purchasing. The key finding is that gamification works through engagement and emotional connection with the retailer rather than by directly incentivizing purchases, which gives a ready-made mechanism for linking gamification to loyalty in food delivery apps; the effect is stronger for younger users. Its engagement scale (trust, satisfaction, willingness to recommend) in fact measures attitudinal loyalty. Although the context is online grocery rather than food delivery and gender differences are descriptive only, the logic transfers.</t>
   </si>
 </sst>
 </file>
